--- a/static/standards-correlations/New_York_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/New_York_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$37</definedName>
@@ -565,10 +565,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | NYS CS and Digital Fluency Learning Standards</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | NYS CS and Digital Fluency Learning Standards</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -602,7 +603,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -1696,7 +1697,7 @@
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Ext 1.1F (Why a PIN?) covers a digital safeguard and Discovery Systems 10 covers behavioural ones. New York's clarifying statement requires the CIA Triad explicitly, which is not taught. Physical safeguards are absent.</t>
+          <t>Ext 1.1F (Why a PIN?) covers a digital safeguard and Introductory Systems 10 covers behavioural ones. New York's clarifying statement requires the CIA Triad explicitly, which is not taught. Physical safeguards are absent.</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1822,7 @@
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>Discovery Systems 10 covers recognising and not acting on a phishing attempt, which is a prior action at elementary level. Breach response planning is not addressed.</t>
+          <t>Introductory Systems 10 covers recognising and not acting on a phishing attempt, which is a prior action at elementary level. Breach response planning is not addressed.</t>
         </is>
       </c>
     </row>
@@ -2113,6 +2114,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -2157,7 +2159,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2171,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -2281,6 +2283,8 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
@@ -2304,7 +2308,7 @@
 SOURCE NOTE: Codes, statements, and clarifying statements transcribed directly from the official NYSED 9-12 standards PDF, not a third-party framework.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?'), or where the standard is only partly met. New York publishes a Clarifying Statement with each standard; those were used to judge intent and are referenced in the Coverage notes where they changed the score.</t>
         </is>
       </c>
